--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.28239039071052</v>
+        <v>6.383388438490461</v>
       </c>
       <c r="D2" t="n">
-        <v>23.04516360418282</v>
+        <v>3.744839085679708</v>
       </c>
       <c r="E2" t="n">
-        <v>9.069843710222329</v>
+        <v>1.473849602911129</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9450538135719118</v>
+        <v>0.1535712447054356</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.14270297026587</v>
+        <v>3.435689232668203</v>
       </c>
       <c r="D3" t="n">
-        <v>21.15505597703899</v>
+        <v>3.437696596268837</v>
       </c>
       <c r="E3" t="n">
-        <v>9.069843710222329</v>
+        <v>1.473849602911129</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9450538135719118</v>
+        <v>0.1535712447054356</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
